--- a/ig/ch-core/StructureDefinition-ch-core-encounter.xlsx
+++ b/ig/ch-core/StructureDefinition-ch-core-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3215" uniqueCount="559">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T08:02:49+00:00</t>
+    <t>2026-06-10T15:05:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1410,6 +1410,19 @@
     <t>Flag to indicate if it is a suspected readmission</t>
   </si>
   <si>
+    <t>Encounter.hospitalization.extension:BfsMsEncounterType</t>
+  </si>
+  <si>
+    <t>BfsMsEncounterType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://fhir.ch/ig/ch-core/StructureDefinition/ch-ext-bfs-ms-encountertype}
+</t>
+  </si>
+  <si>
+    <t>BFS Medizinische Statistik - Liegeklasse (Encounter Type)</t>
+  </si>
+  <si>
     <t>Encounter.hospitalization.extension:BfsDischargeDecision</t>
   </si>
   <si>
@@ -1497,7 +1510,7 @@
     <t>The reason for re-admission of this hospitalization encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092|2.9</t>
   </si>
   <si>
     <t>PV1-13</t>
@@ -2054,7 +2067,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN88"/>
+  <dimension ref="A1:AN89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.984375" customWidth="true" bestFit="true"/>
@@ -9815,43 +9828,41 @@
         <v>455</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="D69" t="s" s="2">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>136</v>
+        <v>457</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>252</v>
+        <v>458</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>83</v>
       </c>
@@ -9899,7 +9910,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>254</v>
+        <v>173</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -9908,7 +9919,7 @@
         <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>83</v>
+        <v>437</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>141</v>
@@ -9928,42 +9939,46 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>83</v>
+        <v>251</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>457</v>
+        <v>252</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
       </c>
@@ -10011,31 +10026,31 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>456</v>
+        <v>254</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>459</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71">
@@ -10066,13 +10081,13 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10141,21 +10156,21 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>464</v>
+        <v>154</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>83</v>
+        <v>463</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10178,7 +10193,7 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>187</v>
+        <v>465</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>466</v>
@@ -10211,11 +10226,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>468</v>
+        <v>83</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10233,7 +10250,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10251,21 +10268,21 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>470</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10291,10 +10308,10 @@
         <v>187</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10321,13 +10338,11 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10345,7 +10360,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10363,21 +10378,21 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>167</v>
+        <v>473</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10388,7 +10403,7 @@
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>83</v>
@@ -10403,17 +10418,13 @@
         <v>187</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>83</v>
       </c>
@@ -10440,10 +10451,10 @@
         <v>284</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10461,13 +10472,13 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>83</v>
@@ -10479,21 +10490,21 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>484</v>
+        <v>167</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10519,13 +10530,17 @@
         <v>187</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
       </c>
@@ -10549,13 +10564,13 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>114</v>
+        <v>284</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -10573,7 +10588,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -10591,21 +10606,21 @@
         <v>83</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10631,10 +10646,10 @@
         <v>187</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10664,10 +10679,10 @@
         <v>114</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -10685,7 +10700,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -10703,21 +10718,21 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10728,7 +10743,7 @@
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -10740,13 +10755,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>461</v>
+        <v>187</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10773,13 +10788,13 @@
         <v>83</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>83</v>
+        <v>500</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>83</v>
+        <v>501</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
@@ -10797,13 +10812,13 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>83</v>
@@ -10815,21 +10830,21 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>504</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10852,13 +10867,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>187</v>
+        <v>465</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10885,13 +10900,13 @@
         <v>83</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>506</v>
+        <v>83</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>508</v>
+        <v>83</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>83</v>
@@ -10909,7 +10924,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -10927,21 +10942,21 @@
         <v>83</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10952,7 +10967,7 @@
         <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>83</v>
@@ -10964,17 +10979,15 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>244</v>
+        <v>187</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -10999,13 +11012,13 @@
         <v>83</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>83</v>
+        <v>510</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>83</v>
@@ -11023,13 +11036,13 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>83</v>
@@ -11041,21 +11054,21 @@
         <v>83</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>83</v>
+        <v>514</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11066,7 +11079,7 @@
         <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>83</v>
@@ -11078,15 +11091,17 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>163</v>
+        <v>244</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>164</v>
+        <v>516</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -11135,25 +11150,25 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>166</v>
+        <v>515</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>167</v>
+        <v>519</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>83</v>
@@ -11164,21 +11179,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>83</v>
@@ -11190,17 +11205,15 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -11249,19 +11262,19 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>83</v>
@@ -11278,14 +11291,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>251</v>
+        <v>135</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11298,26 +11311,24 @@
         <v>83</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>252</v>
+        <v>137</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>253</v>
+        <v>170</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="O82" t="s" s="2">
-        <v>145</v>
-      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>83</v>
       </c>
@@ -11365,7 +11376,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>254</v>
+        <v>173</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11383,7 +11394,7 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>83</v>
@@ -11394,42 +11405,46 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>83</v>
+        <v>251</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>520</v>
+        <v>136</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>521</v>
+        <v>252</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
       </c>
@@ -11477,39 +11492,39 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>519</v>
+        <v>254</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>523</v>
+        <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>354</v>
+        <v>133</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>524</v>
+        <v>83</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>525</v>
+        <v>83</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11517,7 +11532,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>90</v>
@@ -11532,17 +11547,15 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>110</v>
+        <v>524</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -11567,13 +11580,13 @@
         <v>83</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>530</v>
+        <v>83</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>531</v>
+        <v>83</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -11591,10 +11604,10 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>90</v>
@@ -11606,24 +11619,24 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>83</v>
+        <v>527</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>532</v>
+        <v>354</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>83</v>
+        <v>528</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>83</v>
+        <v>529</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11646,16 +11659,16 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11681,13 +11694,13 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>284</v>
+        <v>180</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -11705,7 +11718,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -11723,7 +11736,7 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>83</v>
+        <v>536</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>83</v>
@@ -11734,10 +11747,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11760,15 +11773,17 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -11793,13 +11808,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>83</v>
+        <v>284</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>83</v>
+        <v>541</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>83</v>
+        <v>542</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -11817,7 +11832,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -11835,7 +11850,7 @@
         <v>83</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>83</v>
@@ -11846,10 +11861,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11872,7 +11887,7 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>543</v>
+        <v>218</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>544</v>
@@ -11929,7 +11944,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -11944,24 +11959,24 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>353</v>
+        <v>83</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>546</v>
+        <v>347</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>547</v>
+        <v>83</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11984,17 +11999,15 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="L88" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>552</v>
-      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -12043,7 +12056,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12058,15 +12071,129 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K89" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AL88" t="s" s="2">
+      <c r="L89" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="AM88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN88" t="s" s="2">
+      <c r="M89" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>83</v>
       </c>
     </row>
